--- a/coronavirus_response_forms/021_salon_precaution_agreement_form--coronavirus_response_forms.xlsx
+++ b/coronavirus_response_forms/021_salon_precaution_agreement_form--coronavirus_response_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -814,7 +814,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Employee Date</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -832,12 +832,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>employee_name2</t>
+          <t>employee_name2_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Name of Manager</t>
+          <t>Employee Name2 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -855,7 +855,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>employee_name</t>
+          <t>employee_name_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Name of Manager</t>
+          <t>Manager Name</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -975,7 +975,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Manager Date</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Date (4)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>employee_position</t>
+          <t>employee_position_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Employee Date2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
